--- a/project-management/risks/Risk_Register_SmartParking.xlsx
+++ b/project-management/risks/Risk_Register_SmartParking.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="135">
   <si>
     <t>RISK REGISTER</t>
   </si>
@@ -253,13 +253,13 @@
     <t>Falta de disponibilidad de componentes durante la construcción</t>
   </si>
   <si>
-    <t>Retrasos o dificultades para adquirir sensores, cables u otros componentes</t>
+    <t>Retrasos o dificultades para adquirir sensores, cables u otros componentes.</t>
   </si>
   <si>
     <t>Identificar componentes necesarios con anticipación y considerar alternativas compatibles</t>
   </si>
   <si>
-    <t>Sustituir temporalmente por un componente equivalente o ajustar las pruebas</t>
+    <t>Sustituir temporalmente por un componente equivalente o ajustar las pruebas.</t>
   </si>
   <si>
     <t>R-13</t>
@@ -310,142 +310,112 @@
     <t>R-16</t>
   </si>
   <si>
-    <t>Errores en la interfaz de usuario</t>
-  </si>
-  <si>
-    <t>Errores de diseño, navegación o validación de datos</t>
-  </si>
-  <si>
-    <t>Realizar pruebas de navegación, validación de campos y revisión de pantallas</t>
-  </si>
-  <si>
-    <t>Corregir la interfaz y repetir las pruebas afectadas</t>
+    <t>Dificultad para interpretar los estados de los espacios</t>
+  </si>
+  <si>
+    <t>Estados o indicadores visuales poco claros para el usuario.</t>
+  </si>
+  <si>
+    <t>Definir indicadores claros para disponible, ocupado, reservado y otros estados.</t>
+  </si>
+  <si>
+    <t>Ajustar colores, iconos, textos o distribución de la información.</t>
+  </si>
+  <si>
+    <t>Alberto / Santiago</t>
+  </si>
+  <si>
+    <t>R-17</t>
+  </si>
+  <si>
+    <t>Retraso en actividades del proyecto</t>
+  </si>
+  <si>
+    <t>Subestimación de tiempos, bloqueos técnicos o incumplimiento de tareas.</t>
+  </si>
+  <si>
+    <t>Dar seguimiento al cronograma, actualizar GitHub y reportar bloqueos oportunamente.</t>
+  </si>
+  <si>
+    <t>Reorganizar prioridades, reasignar tareas y actualizar el cronograma.</t>
+  </si>
+  <si>
+    <t>R-18</t>
+  </si>
+  <si>
+    <t>Errores en la configuración del entorno de desarrollo</t>
+  </si>
+  <si>
+    <t>Configuraciones diferentes entre equipos o dependencias incorrectas.</t>
+  </si>
+  <si>
+    <t>Documentar versiones, dependencias y configuración requerida.</t>
+  </si>
+  <si>
+    <t>Reinstalar/configurar el entorno siguiendo la documentación del proyecto.</t>
+  </si>
+  <si>
+    <t>R-19</t>
+  </si>
+  <si>
+    <t>Cambios en la interfaz durante el desarrollo</t>
+  </si>
+  <si>
+    <t>Ajustes derivados de pruebas, retroalimentación o mejoras de navegación.</t>
+  </si>
+  <si>
+    <t>Registrar los cambios y evaluar su impacto antes de implementarlos.</t>
+  </si>
+  <si>
+    <t>Reprogramar el cambio para una iteración posterior si afecta otras actividades.</t>
   </si>
   <si>
     <t>Alberto / Fernando</t>
   </si>
   <si>
-    <t>R-17</t>
-  </si>
-  <si>
-    <t>Consumo elevado de recursos en Raspberry Pi</t>
-  </si>
-  <si>
-    <t>Incremento de sensores, mensajes MQTT o procesos ejecutándose simultáneamente</t>
-  </si>
-  <si>
-    <t>Monitorear CPU, RAM y procesos durante las pruebas</t>
-  </si>
-  <si>
-    <t>Reducir frecuencia de actualización, optimizar procesos o reiniciar servicios</t>
-  </si>
-  <si>
-    <t>R-18</t>
-  </si>
-  <si>
-    <t>Dificultad para interpretar los estados de los espacios</t>
-  </si>
-  <si>
-    <t>Estados o indicadores visuales poco claros para el usuario</t>
-  </si>
-  <si>
-    <t>Definir indicadores claros para disponible, ocupado, reservado y otros estados</t>
-  </si>
-  <si>
-    <t>Ajustar colores, iconos, textos o distribución de la información</t>
-  </si>
-  <si>
-    <t>Alberto / Santiago</t>
-  </si>
-  <si>
-    <t>R-19</t>
-  </si>
-  <si>
-    <t>Retraso en actividades del proyecto</t>
-  </si>
-  <si>
-    <t>Subestimación de tiempos, bloqueos técnicos o incumplimiento de tareas.</t>
-  </si>
-  <si>
-    <t>Dar seguimiento al cronograma, actualizar GitHub Project y reportar bloqueos oportunamente.</t>
-  </si>
-  <si>
-    <t>Reorganizar prioridades, reasignar tareas y actualizar el cronograma.</t>
-  </si>
-  <si>
     <t>R-20</t>
   </si>
   <si>
-    <t>Errores en la configuración del entorno de desarrollo</t>
-  </si>
-  <si>
-    <t>Configuraciones diferentes entre equipos o dependencias incorrectas</t>
-  </si>
-  <si>
-    <t>Documentar versiones, dependencias y configuración requerida</t>
-  </si>
-  <si>
-    <t>Reinstalar/configurar el entorno siguiendo la documentación del proyecto</t>
+    <t>Incompatibilidad de la aplicación con algunos dispositivos</t>
+  </si>
+  <si>
+    <t>Diferencias de versiones, resolución o características del dispositivo.</t>
+  </si>
+  <si>
+    <t>Realizar pruebas en diferentes versiones y tamaños de pantalla.</t>
+  </si>
+  <si>
+    <t>Corregir problemas de compatibilidad y establecer versión mínima soportada.</t>
   </si>
   <si>
     <t>R-21</t>
   </si>
   <si>
-    <t>Cambios menores en la interfaz durante el desarrollo</t>
-  </si>
-  <si>
-    <t>Ajustes derivados de pruebas, retroalimentación o mejoras de navegación</t>
-  </si>
-  <si>
-    <t>Registrar los cambios y evaluar su impacto antes de implementarlos</t>
-  </si>
-  <si>
-    <t>Reprogramar el cambio para una iteración posterior si afecta otras actividades</t>
+    <t>Pérdida de información por falta de respaldos</t>
+  </si>
+  <si>
+    <t>Ausencia de copias de seguridad de la información almacenada.</t>
+  </si>
+  <si>
+    <t>Establecer respaldos periódicos de la base de datos y verificar su recuperación.</t>
+  </si>
+  <si>
+    <t>Restaurar la última copia disponible y recuperar los registros afectados.</t>
   </si>
   <si>
     <t>R-22</t>
   </si>
   <si>
-    <t>Incompatibilidad de la aplicación con algunos dispositivos</t>
-  </si>
-  <si>
-    <t>Diferencias de versiones, resolución o características del dispositivo</t>
-  </si>
-  <si>
-    <t>Realizar pruebas en diferentes versiones y tamaños de pantalla</t>
-  </si>
-  <si>
-    <t>Corregir problemas de compatibilidad y establecer versión mínima soportada</t>
-  </si>
-  <si>
-    <t>R-23</t>
-  </si>
-  <si>
-    <t>Pérdida de información por falta de respaldos</t>
-  </si>
-  <si>
-    <t>Ausencia de copias de seguridad de la información almacenada</t>
-  </si>
-  <si>
-    <t>Establecer respaldos periódicos de la base de datos y verificar su recuperación</t>
-  </si>
-  <si>
-    <t>Restaurar la última copia disponible y recuperar los registros afectados</t>
-  </si>
-  <si>
-    <t>R-24</t>
-  </si>
-  <si>
     <t>Pérdida o desorganización de evidencias y documentación</t>
   </si>
   <si>
-    <t>Archivos almacenados sin estructura o sin control de versiones</t>
-  </si>
-  <si>
-    <t>Mantener documentación y evidencias organizadas en el repositorio</t>
-  </si>
-  <si>
-    <t>Recuperar archivos desde GitHub, copias locales o registros disponibles y reorganizarlos</t>
+    <t>Archivos almacenados sin estructura o sin control de versiones.</t>
+  </si>
+  <si>
+    <t>Mantener documentación y evidencias organizadas en el repositorio.</t>
+  </si>
+  <si>
+    <t>Recuperar archivos desde GitHub, copias locales o registros disponibles y reorganizarlos.</t>
   </si>
 </sst>
 </file>
@@ -717,7 +687,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:M28" displayName="RiskTable" name="RiskTable" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:M26" displayName="RiskTable" name="RiskTable" id="1">
   <tableColumns count="13">
     <tableColumn name="ID" id="1"/>
     <tableColumn name="Riesgo / condición" id="2"/>
@@ -1021,11 +991,11 @@
         <v>5.0</v>
       </c>
       <c r="F5" s="7">
-        <f t="shared" ref="F5:F28" si="1">D5*E5</f>
+        <f t="shared" ref="F5:F26" si="1">D5*E5</f>
         <v>20</v>
       </c>
       <c r="G5" s="8" t="str">
-        <f t="shared" ref="G5:G28" si="2">IF(F5&gt;=15,"Alta",IF(F5&gt;=6,"Media","Baja"))</f>
+        <f t="shared" ref="G5:G26" si="2">IF(F5&gt;=15,"Alta",IF(F5&gt;=6,"Media","Baja"))</f>
         <v>Alta</v>
       </c>
       <c r="H5" s="9" t="s">
@@ -1660,14 +1630,14 @@
         <v>100</v>
       </c>
       <c r="D20" s="6">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E20" s="6">
         <v>3.0</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G20" s="8" t="str">
         <f t="shared" si="2"/>
@@ -1696,25 +1666,25 @@
       <c r="A21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="5" t="s">
         <v>106</v>
       </c>
       <c r="D21" s="6">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E21" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="F21" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="F21" s="7">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G21" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>107</v>
@@ -1723,7 +1693,7 @@
         <v>108</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>21</v>
@@ -1735,7 +1705,7 @@
         <v>46282.0</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22">
       <c r="A22" s="4" t="s">
         <v>109</v>
       </c>
@@ -1749,15 +1719,15 @@
         <v>2.0</v>
       </c>
       <c r="E22" s="6">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F22" s="13">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>112</v>
@@ -1766,7 +1736,7 @@
         <v>113</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>21</v>
@@ -1778,38 +1748,38 @@
         <v>46282.0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="D23" s="6">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="E23" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="F23" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="F23" s="13">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G23" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="H23" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I23" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="J23" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>21</v>
@@ -1835,15 +1805,15 @@
         <v>2.0</v>
       </c>
       <c r="E24" s="6">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>123</v>
@@ -1852,7 +1822,7 @@
         <v>124</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>21</v>
@@ -1878,15 +1848,15 @@
         <v>2.0</v>
       </c>
       <c r="E25" s="6">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G25" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>128</v>
@@ -1895,7 +1865,7 @@
         <v>129</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>21</v>
@@ -1938,7 +1908,7 @@
         <v>134</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>21</v>
@@ -1950,91 +1920,14 @@
         <v>46282.0</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="E27" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="F27" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="G27" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>Media</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M27" s="11">
-        <v>46282.0</v>
-      </c>
-    </row>
+    <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="F28" s="13">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="G28" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>Media</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M28" s="11">
-        <v>46282.0</v>
-      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="M28" s="16"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="C29" s="14"/>
@@ -2068,14 +1961,7 @@
       <c r="G32" s="15"/>
       <c r="M32" s="16"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="M33" s="16"/>
-    </row>
+    <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>
@@ -2086,21 +1972,26 @@
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+    </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="N45" s="16"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="E46" s="19"/>
@@ -2150,12 +2041,7 @@
       <c r="G53" s="19"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="N54" s="16"/>
-    </row>
+    <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1"/>
@@ -3092,29 +2978,28 @@
     <row r="988" ht="15.75" customHeight="1"/>
     <row r="989" ht="15.75" customHeight="1"/>
     <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G28">
+  <conditionalFormatting sqref="G5:G27">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>G5="Alta"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G28">
+  <conditionalFormatting sqref="G5:G27">
     <cfRule type="expression" dxfId="6" priority="2">
       <formula>G5="Media"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G28">
+  <conditionalFormatting sqref="G5:G27">
     <cfRule type="expression" dxfId="7" priority="3">
       <formula>G5="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="K5:K28">
+    <dataValidation type="list" allowBlank="1" sqref="K5:K26">
       <formula1>"Abierto,Mitigando,Materializado,Cerrado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/project-management/risks/Risk_Register_SmartParking.xlsx
+++ b/project-management/risks/Risk_Register_SmartParking.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="145">
   <si>
     <t>RISK REGISTER</t>
   </si>
@@ -76,144 +76,165 @@
     <t>Santiago</t>
   </si>
   <si>
+    <t>Cerrado</t>
+  </si>
+  <si>
+    <t>Issue #18</t>
+  </si>
+  <si>
+    <t>R-02</t>
+  </si>
+  <si>
+    <t>Pérdida o retraso en la comunicación MQTT</t>
+  </si>
+  <si>
+    <t>Interrupciones de red, configuración incorrecta o saturación del broker.</t>
+  </si>
+  <si>
+    <t>Configurar correctamente broker, tópicos y QoS; realizar pruebas de conexión y monitoreo.</t>
+  </si>
+  <si>
+    <t>Reconectar automáticamente y almacenar temporalmente los datos para reenviarlos.</t>
+  </si>
+  <si>
+    <t>Issue #28</t>
+  </si>
+  <si>
+    <t>R-03</t>
+  </si>
+  <si>
+    <t>Conflicto de reservas sobre un mismo espacio</t>
+  </si>
+  <si>
+    <t>Dos usuarios intentan reservar el mismo espacio simultáneamente.</t>
+  </si>
+  <si>
+    <t>Verificar disponibilidad nuevamente antes de confirmar y utilizar estados temporales de reserva.</t>
+  </si>
+  <si>
+    <t>Cancelar la operación duplicada y liberar el espacio para permitir una nueva reserva.</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>Issue #27</t>
+  </si>
+  <si>
+    <t>R-04</t>
+  </si>
+  <si>
+    <t>Falla en el servicio de pagos</t>
+  </si>
+  <si>
+    <t>Indisponibilidad o errores de la plataforma de pagos externa.</t>
+  </si>
+  <si>
+    <t>Validar respuestas de la API, manejar errores y no confirmar una reserva hasta validar el pago.</t>
+  </si>
+  <si>
+    <t>Mantener la reserva pendiente y permitir reintentar el pago cuando el servicio esté disponible.</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>Mitigando</t>
+  </si>
+  <si>
+    <t>Issue #32</t>
+  </si>
+  <si>
+    <t>R-05</t>
+  </si>
+  <si>
+    <t>Pérdida de conexión con Supabase</t>
+  </si>
+  <si>
+    <t>Fallas de Internet, servicio no disponible o errores de conexión.</t>
+  </si>
+  <si>
+    <t>Implementar manejo de errores, reconexión y validación de respuestas del servicio.</t>
+  </si>
+  <si>
+    <t>Reintentar conexión y conservar temporalmente los datos necesarios hasta recuperar el servicio.</t>
+  </si>
+  <si>
+    <t>Issue #26</t>
+  </si>
+  <si>
+    <t>R-06</t>
+  </si>
+  <si>
+    <t>Fallas de comunicación entre hardware y software</t>
+  </si>
+  <si>
+    <t>Errores en protocolos, configuración, conexiones o procesamiento de datos.</t>
+  </si>
+  <si>
+    <t>Definir protocolos y formatos de datos, además de realizar pruebas de integración progresivas.</t>
+  </si>
+  <si>
+    <t>Aislar el componente que presenta la falla y utilizar comunicación local/manual para diagnóstico.</t>
+  </si>
+  <si>
+    <t>R-07</t>
+  </si>
+  <si>
+    <t>Sobrecarga del sistema al aumentar sensores o usuarios</t>
+  </si>
+  <si>
+    <t>Incremento de conexiones, mensajes MQTT o solicitudes al backend.</t>
+  </si>
+  <si>
+    <t>Realizar pruebas de carga y monitorear CPU, memoria, conexiones y tiempos de respuesta.</t>
+  </si>
+  <si>
+    <t>Reducir temporalmente la frecuencia de actualización y optimizar servicios o recursos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando </t>
+  </si>
+  <si>
+    <t>R-08</t>
+  </si>
+  <si>
+    <t>Vulnerabilidad o acceso no autorizado a los datos</t>
+  </si>
+  <si>
+    <t>Configuración insegura, credenciales expuestas o validaciones insuficientes.</t>
+  </si>
+  <si>
+    <t>Utilizar autenticación, JWT, HTTPS, control de roles y protección de credenciales.</t>
+  </si>
+  <si>
+    <t>Revocar credenciales comprometidas, bloquear accesos afectados y corregir la vulnerabilidad.</t>
+  </si>
+  <si>
+    <t>R-09</t>
+  </si>
+  <si>
+    <t>Usuario no se presenta a su reserva</t>
+  </si>
+  <si>
+    <t>El usuario reserva un espacio y no llega dentro del periodo establecido.</t>
+  </si>
+  <si>
+    <t>Establecer límite de tiempo para conservar una reserva y enviar recordatorios.</t>
+  </si>
+  <si>
+    <t>Liberar automáticamente el espacio después del tiempo establecido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberto </t>
+  </si>
+  <si>
     <t>Abierto</t>
   </si>
   <si>
     <t>Pendiente de asignar ISSUE</t>
   </si>
   <si>
-    <t>R-02</t>
-  </si>
-  <si>
-    <t>Pérdida o retraso en la comunicación MQTT</t>
-  </si>
-  <si>
-    <t>Interrupciones de red, configuración incorrecta o saturación del broker.</t>
-  </si>
-  <si>
-    <t>Configurar correctamente broker, tópicos y QoS; realizar pruebas de conexión y monitoreo.</t>
-  </si>
-  <si>
-    <t>Reconectar automáticamente y almacenar temporalmente los datos para reenviarlos.</t>
-  </si>
-  <si>
-    <t>R-03</t>
-  </si>
-  <si>
-    <t>Conflicto de reservas sobre un mismo espacio</t>
-  </si>
-  <si>
-    <t>Dos usuarios intentan reservar el mismo espacio simultáneamente.</t>
-  </si>
-  <si>
-    <t>Verificar disponibilidad nuevamente antes de confirmar y utilizar estados temporales de reserva.</t>
-  </si>
-  <si>
-    <t>Cancelar la operación duplicada y liberar el espacio para permitir una nueva reserva.</t>
-  </si>
-  <si>
-    <t>Alberto</t>
-  </si>
-  <si>
-    <t>R-04</t>
-  </si>
-  <si>
-    <t>Falla en el servicio de pagos</t>
-  </si>
-  <si>
-    <t>Indisponibilidad o errores de la plataforma de pagos externa.</t>
-  </si>
-  <si>
-    <t>Validar respuestas de la API, manejar errores y no confirmar una reserva hasta validar el pago.</t>
-  </si>
-  <si>
-    <t>Mantener la reserva pendiente y permitir reintentar el pago cuando el servicio esté disponible.</t>
-  </si>
-  <si>
-    <t>Fernando</t>
-  </si>
-  <si>
-    <t>R-05</t>
-  </si>
-  <si>
-    <t>Pérdida de conexión con Supabase</t>
-  </si>
-  <si>
-    <t>Fallas de Internet, servicio no disponible o errores de conexión.</t>
-  </si>
-  <si>
-    <t>Implementar manejo de errores, reconexión y validación de respuestas del servicio.</t>
-  </si>
-  <si>
-    <t>Reintentar conexión y conservar temporalmente los datos necesarios hasta recuperar el servicio.</t>
-  </si>
-  <si>
-    <t>R-06</t>
-  </si>
-  <si>
-    <t>Fallas de comunicación entre hardware y software</t>
-  </si>
-  <si>
-    <t>Errores en protocolos, configuración, conexiones o procesamiento de datos.</t>
-  </si>
-  <si>
-    <t>Definir protocolos y formatos de datos, además de realizar pruebas de integración progresivas.</t>
-  </si>
-  <si>
-    <t>Aislar el componente que presenta la falla y utilizar comunicación local/manual para diagnóstico.</t>
-  </si>
-  <si>
-    <t>R-07</t>
-  </si>
-  <si>
-    <t>Sobrecarga del sistema al aumentar sensores o usuarios</t>
-  </si>
-  <si>
-    <t>Incremento de conexiones, mensajes MQTT o solicitudes al backend.</t>
-  </si>
-  <si>
-    <t>Realizar pruebas de carga y monitorear CPU, memoria, conexiones y tiempos de respuesta.</t>
-  </si>
-  <si>
-    <t>Reducir temporalmente la frecuencia de actualización y optimizar servicios o recursos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernando </t>
-  </si>
-  <si>
-    <t>R-08</t>
-  </si>
-  <si>
-    <t>Vulnerabilidad o acceso no autorizado a los datos</t>
-  </si>
-  <si>
-    <t>Configuración insegura, credenciales expuestas o validaciones insuficientes.</t>
-  </si>
-  <si>
-    <t>Utilizar autenticación, JWT, HTTPS, control de roles y protección de credenciales.</t>
-  </si>
-  <si>
-    <t>Revocar credenciales comprometidas, bloquear accesos afectados y corregir la vulnerabilidad.</t>
-  </si>
-  <si>
-    <t>R-09</t>
-  </si>
-  <si>
-    <t>Usuario no se presenta a su reserva</t>
-  </si>
-  <si>
-    <t>El usuario reserva un espacio y no llega dentro del periodo establecido.</t>
-  </si>
-  <si>
-    <t>Establecer límite de tiempo para conservar una reserva y enviar recordatorios.</t>
-  </si>
-  <si>
-    <t>Liberar automáticamente el espacio después del tiempo establecido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alberto </t>
-  </si>
-  <si>
     <t>R-10</t>
   </si>
   <si>
@@ -277,6 +298,9 @@
     <t>Corregir registros afectados y recuperar información mediante respaldos cuando sea necesario.</t>
   </si>
   <si>
+    <t>Issue #22</t>
+  </si>
+  <si>
     <t>R-14</t>
   </si>
   <si>
@@ -307,6 +331,9 @@
     <t>Marcar la disponibilidad como no confiable/pendiente y actualizarla al recuperar la comunicación.</t>
   </si>
   <si>
+    <t>Santiago / Fernando</t>
+  </si>
+  <si>
     <t>R-16</t>
   </si>
   <si>
@@ -416,6 +443,9 @@
   </si>
   <si>
     <t>Recuperar archivos desde GitHub, copias locales o registros disponibles y reorganizarlos.</t>
+  </si>
+  <si>
+    <t>Issue #37</t>
   </si>
 </sst>
 </file>
@@ -502,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -535,6 +565,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1007,14 +1040,14 @@
       <c r="J5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="M5" s="11">
-        <v>46282.0</v>
+        <v>46313.0</v>
       </c>
     </row>
     <row r="6">
@@ -1050,25 +1083,25 @@
       <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="11">
-        <v>46282.0</v>
+        <v>28</v>
+      </c>
+      <c r="M6" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6">
         <v>3.0</v>
@@ -1085,33 +1118,33 @@
         <v>Alta</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" s="11">
-        <v>46282.0</v>
+        <v>35</v>
+      </c>
+      <c r="M7" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="6">
         <v>3.0</v>
@@ -1128,33 +1161,33 @@
         <v>Alta</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="11">
-        <v>46282.0</v>
+        <v>43</v>
+      </c>
+      <c r="M8" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" s="6">
         <v>3.0</v>
@@ -1171,33 +1204,33 @@
         <v>Alta</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="11">
-        <v>46282.0</v>
+        <v>49</v>
+      </c>
+      <c r="M9" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D10" s="6">
         <v>3.0</v>
@@ -1214,33 +1247,33 @@
         <v>Alta</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="11">
-        <v>46282.0</v>
+        <v>28</v>
+      </c>
+      <c r="M10" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D11" s="6">
         <v>3.0</v>
@@ -1257,33 +1290,33 @@
         <v>Media</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>21</v>
+        <v>60</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="11">
-        <v>46282.0</v>
+      <c r="M11" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D12" s="6">
         <v>3.0</v>
@@ -1300,33 +1333,33 @@
         <v>Alta</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>21</v>
+      <c r="K12" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="11">
-        <v>46282.0</v>
+        <v>49</v>
+      </c>
+      <c r="M12" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D13" s="6">
         <v>3.0</v>
@@ -1343,33 +1376,33 @@
         <v>Media</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M13" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D14" s="6">
         <v>3.0</v>
@@ -1386,33 +1419,33 @@
         <v>Media</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M14" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D15" s="6">
         <v>3.0</v>
@@ -1429,33 +1462,33 @@
         <v>Media</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M15" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>79</v>
+        <v>85</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D16" s="6">
         <v>2.0</v>
@@ -1463,7 +1496,7 @@
       <c r="E16" s="6">
         <v>3.0</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1472,33 +1505,33 @@
         <v>Media</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M16" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D17" s="6">
         <v>3.0</v>
@@ -1515,33 +1548,33 @@
         <v>Alta</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" s="11">
-        <v>46282.0</v>
+        <v>95</v>
+      </c>
+      <c r="M17" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D18" s="6">
         <v>3.0</v>
@@ -1558,33 +1591,33 @@
         <v>Media</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M18" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D19" s="6">
         <v>4.0</v>
@@ -1601,33 +1634,33 @@
         <v>Alta</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M19" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>99</v>
+        <v>107</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D20" s="6">
         <v>2.0</v>
@@ -1635,7 +1668,7 @@
       <c r="E20" s="6">
         <v>3.0</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1644,33 +1677,33 @@
         <v>Media</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K20" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="11">
-        <v>46282.0</v>
+      <c r="M20" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D21" s="6">
         <v>4.0</v>
@@ -1687,33 +1720,33 @@
         <v>Alta</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M21" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>110</v>
+        <v>118</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>119</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D22" s="6">
         <v>2.0</v>
@@ -1721,7 +1754,7 @@
       <c r="E22" s="6">
         <v>2.0</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -1730,33 +1763,33 @@
         <v>Baja</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M22" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>115</v>
+        <v>123</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D23" s="6">
         <v>3.0</v>
@@ -1764,7 +1797,7 @@
       <c r="E23" s="6">
         <v>3.0</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -1773,33 +1806,33 @@
         <v>Media</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>21</v>
+        <v>128</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M23" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M23" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>121</v>
+        <v>129</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D24" s="6">
         <v>2.0</v>
@@ -1807,7 +1840,7 @@
       <c r="E24" s="6">
         <v>3.0</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1816,33 +1849,33 @@
         <v>Media</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>21</v>
+        <v>71</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M24" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D25" s="6">
         <v>2.0</v>
@@ -1850,7 +1883,7 @@
       <c r="E25" s="6">
         <v>4.0</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -1859,33 +1892,33 @@
         <v>Media</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M25" s="11">
-        <v>46282.0</v>
+        <v>73</v>
+      </c>
+      <c r="M25" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>131</v>
+        <v>139</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D26" s="6">
         <v>2.0</v>
@@ -1893,7 +1926,7 @@
       <c r="E26" s="6">
         <v>3.0</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1902,64 +1935,64 @@
         <v>Media</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M26" s="11">
-        <v>46282.0</v>
+        <v>144</v>
+      </c>
+      <c r="M26" s="12">
+        <v>46313.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="M28" s="16"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="M28" s="17"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="M29" s="16"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="M29" s="17"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="M30" s="16"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="M30" s="17"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="M31" s="16"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="M31" s="17"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="C32" s="14"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="M32" s="16"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="M32" s="17"/>
     </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -1973,73 +2006,73 @@
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1"/>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="N45" s="16"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="N46" s="16"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="N46" s="17"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="N47" s="16"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="N47" s="17"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="N48" s="16"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="N48" s="17"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="N49" s="16"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="N49" s="17"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="N50" s="16"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="N50" s="17"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="N51" s="16"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="N51" s="17"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="N52" s="16"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="N52" s="17"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="N53" s="16"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="N53" s="17"/>
     </row>
     <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1"/>
